--- a/dcf/TDG.xlsx
+++ b/dcf/TDG.xlsx
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1119,25 +1119,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.05381579395995244</v>
+        <v>0.05369713073662154</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05881579395995244</v>
+        <v>0.05869713073662153</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.06381579395995243</v>
+        <v>0.06369713073662153</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06881579395995244</v>
+        <v>0.06869713073662154</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.07381579395995244</v>
+        <v>0.07369713073662154</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07881579395995243</v>
+        <v>0.07869713073662153</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.08381579395995244</v>
+        <v>0.08369713073662154</v>
       </c>
     </row>
     <row r="5">
@@ -1145,25 +1145,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>658.6255490018489</v>
+        <v>659.6744993478952</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>615.4988756780007</v>
+        <v>616.4985608738699</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>574.3913955735044</v>
+        <v>575.3444167235951</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>535.1967868854335</v>
+        <v>536.1055946717884</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>497.8148609027801</v>
+        <v>498.6817649887404</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>462.1511795284942</v>
+        <v>462.9783573322213</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>428.1166983707258</v>
+        <v>428.9062032535426</v>
       </c>
     </row>
     <row r="6">
@@ -1171,25 +1171,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>732.2021688625522</v>
+        <v>733.3340203050888</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>685.6739297170609</v>
+        <v>686.7523097462921</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>641.3370708583639</v>
+        <v>642.3648123261175</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>599.0758057160017</v>
+        <v>600.0555772828715</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>558.7810418463592</v>
+        <v>559.7153582623181</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>520.3499628036743</v>
+        <v>521.241194498983</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>483.6856379965162</v>
+        <v>484.5360200321746</v>
       </c>
     </row>
     <row r="7">
@@ -1197,25 +1197,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>805.7787887232557</v>
+        <v>806.9935412622818</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>755.8489837561211</v>
+        <v>757.0060586187141</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>708.2827461432231</v>
+        <v>709.3852079286396</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>662.95482454657</v>
+        <v>664.0055598939543</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>619.7472227899384</v>
+        <v>620.7489515358958</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>578.5487460788548</v>
+        <v>579.5040316657448</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>539.2545776223067</v>
+        <v>540.1658368108064</v>
       </c>
     </row>
     <row r="8">
@@ -1223,25 +1223,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>879.3554085839588</v>
+        <v>880.6530622194751</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>826.024037795181</v>
+        <v>827.2598074911363</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>775.2284214280826</v>
+        <v>776.4056035311619</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>726.8338433771381</v>
+        <v>727.9555425050374</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>680.7134037335172</v>
+        <v>681.7825448094733</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>636.747529354035</v>
+        <v>637.7668688325067</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>594.8235172480969</v>
+        <v>595.7956535894382</v>
       </c>
     </row>
     <row r="9">
@@ -1249,25 +1249,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>952.9320284446624</v>
+        <v>954.3125831766687</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>896.199091834241</v>
+        <v>897.5135563635586</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>842.1740967129421</v>
+        <v>843.4259991336843</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>790.7128622077066</v>
+        <v>791.9055251161205</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>741.6795846770964</v>
+        <v>742.816138083051</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>694.9463126292154</v>
+        <v>696.0297059992685</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>650.3924568738876</v>
+        <v>651.4254703680703</v>
       </c>
     </row>
     <row r="10">
@@ -1275,25 +1275,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>1026.508648305366</v>
+        <v>1027.972104133862</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>966.3741458733012</v>
+        <v>967.7673052359805</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>909.1197719978015</v>
+        <v>910.4463947362067</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>854.5918810382748</v>
+        <v>855.8555077272036</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>802.6457656206754</v>
+        <v>803.8497313566287</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>753.1450959043956</v>
+        <v>754.2925431660304</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>705.9613964996777</v>
+        <v>707.055287146702</v>
       </c>
     </row>
     <row r="11">
@@ -1301,25 +1301,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>1100.085268166069</v>
+        <v>1101.631625091055</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>1036.549199912361</v>
+        <v>1038.021054108403</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>976.065447282661</v>
+        <v>977.466790338729</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>918.4708998688433</v>
+        <v>919.8054903382869</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>863.6119465642546</v>
+        <v>864.8833246302064</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>811.3438791795758</v>
+        <v>812.5553803327924</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>761.5303361254684</v>
+        <v>762.6851039253338</v>
       </c>
     </row>
     <row r="13">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>1348.489990234375</v>
+        <v>1332.359985351562</v>
       </c>
     </row>
     <row r="14">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06881579395995244</v>
+        <v>0.06869713073662154</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.8880974986527729</v>
+        <v>0.8882001123485016</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24456,7 +24456,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>1348.489990234375</v>
+        <v>1332.359985351562</v>
       </c>
     </row>
     <row r="49">
@@ -24618,13 +24618,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>726.8338433771381</v>
+        <v>727.9555425050374</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>1167.536758353891</v>
+        <v>1169.11776331478</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>395.6522256938101</v>
+        <v>396.432767064885</v>
       </c>
     </row>
     <row r="59">
